--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
   <si>
     <t>Table 1</t>
   </si>
@@ -109,9 +109,15 @@
     <t>beq</t>
   </si>
   <si>
+    <t>`ALUOp_SUB</t>
+  </si>
+  <si>
     <t>bne</t>
   </si>
   <si>
+    <t>`ALUOp_BNE</t>
+  </si>
+  <si>
     <t>j</t>
   </si>
   <si>
@@ -206,9 +212,6 @@
   </si>
   <si>
     <t>sub</t>
-  </si>
-  <si>
-    <t>`ALUOp_SUB</t>
   </si>
   <si>
     <t>subu</t>
@@ -509,7 +512,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -559,6 +562,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1984,19 +1993,37 @@
       <c r="E9" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="18"/>
+      <c r="F9" s="17">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17">
+        <v>0</v>
+      </c>
+      <c r="H9" s="17">
+        <v>1</v>
+      </c>
+      <c r="I9" s="17">
+        <v>0</v>
+      </c>
+      <c r="J9" s="17">
+        <v>0</v>
+      </c>
+      <c r="K9" s="17">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s" s="13">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s" s="13">
+        <v>19</v>
+      </c>
+      <c r="N9" t="s" s="15">
+        <v>32</v>
+      </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" t="s" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="12">
         <v>5</v>
@@ -2010,19 +2037,37 @@
       <c r="E10" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="18"/>
+      <c r="F10" s="17">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17">
+        <v>1</v>
+      </c>
+      <c r="I10" s="17">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17">
+        <v>0</v>
+      </c>
+      <c r="K10" s="17">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s" s="13">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s" s="13">
+        <v>19</v>
+      </c>
+      <c r="N10" t="s" s="15">
+        <v>34</v>
+      </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" t="s" s="11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" s="12">
         <v>2</v>
@@ -2036,19 +2081,37 @@
       <c r="E11" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="18"/>
+      <c r="F11" s="17">
+        <v>1</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14">
+        <v>0</v>
+      </c>
+      <c r="L11" s="14">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0</v>
+      </c>
+      <c r="N11" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" t="s" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12">
         <v>3</v>
@@ -2062,19 +2125,19 @@
       <c r="E12" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" t="s" s="11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12">
         <v>0</v>
@@ -2088,19 +2151,19 @@
       <c r="E13" s="14">
         <v>8</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="20"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" t="s" s="11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12">
         <v>24</v>
@@ -2114,19 +2177,19 @@
       <c r="E14" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="s" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="12">
         <v>25</v>
@@ -2140,19 +2203,19 @@
       <c r="E15" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="18"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="20"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" t="s" s="11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="12">
         <v>30</v>
@@ -2166,22 +2229,22 @@
       <c r="E16" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="20"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="s" s="11">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s" s="16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s" s="13">
         <v>16</v>
@@ -2192,19 +2255,19 @@
       <c r="E17" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="18"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="20"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="s" s="11">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" s="12">
         <v>23</v>
@@ -2218,19 +2281,19 @@
       <c r="E18" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="20"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" s="12">
         <v>0</v>
@@ -2269,12 +2332,12 @@
         <v>19</v>
       </c>
       <c r="N19" t="s" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="12">
         <v>0</v>
@@ -2313,15 +2376,15 @@
         <v>19</v>
       </c>
       <c r="N20" t="s" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s" s="16">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s" s="13">
         <v>16</v>
@@ -2357,12 +2420,12 @@
         <v>30</v>
       </c>
       <c r="N21" t="s" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" s="12">
         <v>0</v>
@@ -2374,24 +2437,24 @@
         <v>16</v>
       </c>
       <c r="E22" t="s" s="13">
-        <v>49</v>
-      </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="18"/>
+        <v>51</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="20"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="11">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s" s="16">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s" s="13">
         <v>16</v>
@@ -2402,22 +2465,22 @@
       <c r="E23" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="18"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="20"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="11">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s" s="16">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s" s="13">
         <v>16</v>
@@ -2428,19 +2491,19 @@
       <c r="E24" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="18"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="20"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="11">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B25" s="12">
         <v>0</v>
@@ -2452,21 +2515,21 @@
         <v>16</v>
       </c>
       <c r="E25" t="s" s="13">
-        <v>55</v>
-      </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="18"/>
+        <v>57</v>
+      </c>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="20"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="11">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" s="12">
         <v>0</v>
@@ -2505,12 +2568,12 @@
         <v>19</v>
       </c>
       <c r="N26" t="s" s="15">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="11">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="12">
         <v>0</v>
@@ -2549,12 +2612,12 @@
         <v>19</v>
       </c>
       <c r="N27" t="s" s="15">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="11">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B28" s="12">
         <v>28</v>
@@ -2568,19 +2631,19 @@
       <c r="E28" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="18"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="20"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="11">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B29" s="12">
         <v>38</v>
@@ -2594,19 +2657,19 @@
       <c r="E29" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="18"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="20"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="11">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B30" s="12">
         <v>29</v>
@@ -2620,22 +2683,22 @@
       <c r="E30" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="18"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="20"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="11">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s" s="16">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s" s="13">
         <v>16</v>
@@ -2646,19 +2709,19 @@
       <c r="E31" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="18"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="20"/>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" t="s" s="11">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B32" s="12">
         <v>0</v>
@@ -2697,12 +2760,12 @@
         <v>19</v>
       </c>
       <c r="N32" t="s" s="15">
-        <v>65</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" t="s" s="11">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" s="12">
         <v>0</v>
@@ -2741,600 +2804,600 @@
         <v>19</v>
       </c>
       <c r="N33" t="s" s="15">
-        <v>65</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="19"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="18"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="20"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="19"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="18"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="20"/>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="19"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="18"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="20"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="18"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="20"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="18"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="20"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="18"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="20"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="18"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="20"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="18"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="20"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="18"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="20"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="19"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="18"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="20"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="18"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="20"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="19"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="18"/>
+      <c r="A45" s="21"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="19"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="18"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="20"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="19"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="18"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="20"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="19"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="18"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="20"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="19"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="18"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="20"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="19"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="18"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="19"/>
+      <c r="N50" s="20"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="19"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="18"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="20"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="19"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="18"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="20"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="19"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="18"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="19"/>
+      <c r="L53" s="19"/>
+      <c r="M53" s="19"/>
+      <c r="N53" s="20"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="19"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="18"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
+      <c r="M54" s="19"/>
+      <c r="N54" s="20"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="19"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="18"/>
+      <c r="A55" s="21"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="19"/>
+      <c r="M55" s="19"/>
+      <c r="N55" s="20"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="19"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="18"/>
+      <c r="A56" s="21"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="19"/>
+      <c r="M56" s="19"/>
+      <c r="N56" s="20"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="19"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="18"/>
+      <c r="A57" s="21"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="19"/>
+      <c r="M57" s="19"/>
+      <c r="N57" s="20"/>
     </row>
     <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="19"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="18"/>
+      <c r="A58" s="21"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="19"/>
+      <c r="M58" s="19"/>
+      <c r="N58" s="20"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="19"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="18"/>
+      <c r="A59" s="21"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="19"/>
+      <c r="M59" s="19"/>
+      <c r="N59" s="20"/>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="19"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="18"/>
+      <c r="A60" s="21"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="19"/>
+      <c r="M60" s="19"/>
+      <c r="N60" s="20"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="19"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="18"/>
+      <c r="A61" s="21"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="19"/>
+      <c r="M61" s="19"/>
+      <c r="N61" s="20"/>
     </row>
     <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="19"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="18"/>
+      <c r="A62" s="21"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19"/>
+      <c r="M62" s="19"/>
+      <c r="N62" s="20"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="19"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="18"/>
+      <c r="A63" s="21"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
+      <c r="M63" s="19"/>
+      <c r="N63" s="20"/>
     </row>
     <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="19"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
-      <c r="L64" s="17"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="18"/>
+      <c r="A64" s="21"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="20"/>
     </row>
     <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="19"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="18"/>
+      <c r="A65" s="21"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="20"/>
     </row>
     <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="19"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="18"/>
+      <c r="A66" s="21"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="20"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="19"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="18"/>
+      <c r="A67" s="21"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="19"/>
+      <c r="M67" s="19"/>
+      <c r="N67" s="20"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="19"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
-      <c r="M68" s="17"/>
-      <c r="N68" s="18"/>
+      <c r="A68" s="21"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
+      <c r="L68" s="19"/>
+      <c r="M68" s="19"/>
+      <c r="N68" s="20"/>
     </row>
     <row r="69" ht="19.5" customHeight="1">
-      <c r="A69" s="19"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
-      <c r="L69" s="17"/>
-      <c r="M69" s="17"/>
-      <c r="N69" s="18"/>
+      <c r="A69" s="21"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="19"/>
+      <c r="M69" s="19"/>
+      <c r="N69" s="20"/>
     </row>
     <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="21"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
-      <c r="J70" s="23"/>
-      <c r="K70" s="23"/>
-      <c r="L70" s="23"/>
-      <c r="M70" s="23"/>
-      <c r="N70" s="24"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="25"/>
+      <c r="L70" s="25"/>
+      <c r="M70" s="25"/>
+      <c r="N70" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="73">
   <si>
     <t>Table 1</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>jal</t>
+  </si>
+  <si>
+    <t>`ALUOp_IN1</t>
   </si>
   <si>
     <t>`SpecialOP_JAL</t>
@@ -295,7 +298,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -507,6 +510,36 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="11"/>
       </left>
       <right style="thin">
@@ -571,7 +604,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -632,6 +665,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -644,16 +683,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2199,7 +2238,7 @@
       <c r="M11" s="17">
         <v>0</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="20">
         <v>0</v>
       </c>
       <c r="O11" t="s" s="13">
@@ -2225,8 +2264,8 @@
       <c r="F12" s="17">
         <v>1</v>
       </c>
-      <c r="G12" s="17">
-        <v>0</v>
+      <c r="G12" t="s" s="16">
+        <v>18</v>
       </c>
       <c r="H12" s="17">
         <v>0</v>
@@ -2238,24 +2277,24 @@
         <v>0</v>
       </c>
       <c r="K12" s="17">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="L12" t="s" s="16">
+        <v>19</v>
       </c>
       <c r="M12" s="17">
         <v>0</v>
       </c>
-      <c r="N12" s="17">
-        <v>0</v>
+      <c r="N12" t="s" s="21">
+        <v>39</v>
       </c>
       <c r="O12" t="s" s="13">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" t="s" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="15">
         <v>0</v>
@@ -2272,37 +2311,21 @@
       <c r="F13" s="17">
         <v>1</v>
       </c>
-      <c r="G13" s="17">
-        <v>0</v>
-      </c>
-      <c r="H13" s="17">
-        <v>0</v>
-      </c>
-      <c r="I13" s="17">
-        <v>0</v>
-      </c>
-      <c r="J13" s="17">
-        <v>0</v>
-      </c>
-      <c r="K13" s="17">
-        <v>0</v>
-      </c>
-      <c r="L13" s="17">
-        <v>0</v>
-      </c>
-      <c r="M13" s="17">
-        <v>0</v>
-      </c>
-      <c r="N13" s="17">
-        <v>0</v>
-      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="11"/>
       <c r="O13" t="s" s="13">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" t="s" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="15">
         <v>24</v>
@@ -2316,20 +2339,20 @@
       <c r="E14" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="s" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="15">
         <v>25</v>
@@ -2343,20 +2366,20 @@
       <c r="E15" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="21"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="23"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" t="s" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="15">
         <v>30</v>
@@ -2370,23 +2393,23 @@
       <c r="E16" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="23"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="s" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s" s="18">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s" s="16">
         <v>17</v>
@@ -2397,20 +2420,20 @@
       <c r="E17" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="21"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="23"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="s" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="15">
         <v>23</v>
@@ -2424,20 +2447,20 @@
       <c r="E18" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="21"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="23"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="15">
         <v>0</v>
@@ -2476,13 +2499,13 @@
         <v>20</v>
       </c>
       <c r="N19" t="s" s="16">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O19" s="13"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="15">
         <v>0</v>
@@ -2521,16 +2544,16 @@
         <v>20</v>
       </c>
       <c r="N20" t="s" s="16">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O20" s="13"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s" s="18">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s" s="16">
         <v>17</v>
@@ -2566,13 +2589,13 @@
         <v>32</v>
       </c>
       <c r="N21" t="s" s="16">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O21" s="13"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="15">
         <v>0</v>
@@ -2584,25 +2607,25 @@
         <v>17</v>
       </c>
       <c r="E22" t="s" s="16">
-        <v>55</v>
-      </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="21"/>
+        <v>56</v>
+      </c>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s" s="18">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s" s="16">
         <v>17</v>
@@ -2613,23 +2636,23 @@
       <c r="E23" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="21"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="23"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="14">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s" s="18">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s" s="16">
         <v>17</v>
@@ -2640,20 +2663,20 @@
       <c r="E24" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="21"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="23"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>
@@ -2665,22 +2688,22 @@
         <v>17</v>
       </c>
       <c r="E25" t="s" s="16">
-        <v>61</v>
-      </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="21"/>
+        <v>62</v>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="23"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="15">
         <v>0</v>
@@ -2719,13 +2742,13 @@
         <v>20</v>
       </c>
       <c r="N26" t="s" s="16">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O26" s="13"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="15">
         <v>0</v>
@@ -2764,13 +2787,13 @@
         <v>20</v>
       </c>
       <c r="N27" t="s" s="16">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O27" s="13"/>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="15">
         <v>28</v>
@@ -2784,20 +2807,20 @@
       <c r="E28" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="21"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="23"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" s="15">
         <v>38</v>
@@ -2811,20 +2834,20 @@
       <c r="E29" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="21"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="23"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" s="15">
         <v>29</v>
@@ -2838,23 +2861,23 @@
       <c r="E30" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="21"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="23"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s" s="18">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s" s="16">
         <v>17</v>
@@ -2865,20 +2888,20 @@
       <c r="E31" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="23"/>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" t="s" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="15">
         <v>0</v>
@@ -2923,7 +2946,7 @@
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" t="s" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" s="15">
         <v>0</v>
@@ -2967,633 +2990,633 @@
       <c r="O33" s="13"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="22"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="21"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="23"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="21"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="23"/>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="22"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="21"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="23"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="21"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="23"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="22"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="21"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="23"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="22"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="21"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="23"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="22"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="21"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="23"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="22"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="21"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="23"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="22"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="21"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="23"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="22"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="21"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="23"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="22"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="21"/>
+      <c r="A44" s="24"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="23"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="22"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="21"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="23"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="22"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="20"/>
-      <c r="O46" s="21"/>
+      <c r="A46" s="24"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="23"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="22"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="21"/>
+      <c r="A47" s="24"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="23"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="22"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20"/>
-      <c r="N48" s="20"/>
-      <c r="O48" s="21"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="23"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="22"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="21"/>
+      <c r="A49" s="24"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="23"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="22"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="21"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="23"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="22"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="21"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="22"/>
+      <c r="N51" s="22"/>
+      <c r="O51" s="23"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="22"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-      <c r="O52" s="21"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="23"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="22"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="20"/>
-      <c r="N53" s="20"/>
-      <c r="O53" s="21"/>
+      <c r="A53" s="24"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
+      <c r="O53" s="23"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="22"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="21"/>
+      <c r="A54" s="24"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+      <c r="N54" s="22"/>
+      <c r="O54" s="23"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20"/>
-      <c r="N55" s="20"/>
-      <c r="O55" s="21"/>
+      <c r="A55" s="24"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="22"/>
+      <c r="N55" s="22"/>
+      <c r="O55" s="23"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="22"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="20"/>
-      <c r="O56" s="21"/>
+      <c r="A56" s="24"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="22"/>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="22"/>
+      <c r="M56" s="22"/>
+      <c r="N56" s="22"/>
+      <c r="O56" s="23"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="20"/>
-      <c r="O57" s="21"/>
+      <c r="A57" s="24"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="22"/>
+      <c r="N57" s="22"/>
+      <c r="O57" s="23"/>
     </row>
     <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="20"/>
-      <c r="O58" s="21"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+      <c r="O58" s="23"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="22"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="21"/>
+      <c r="A59" s="24"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+      <c r="N59" s="22"/>
+      <c r="O59" s="23"/>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="21"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+      <c r="N60" s="22"/>
+      <c r="O60" s="23"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="22"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
-      <c r="K61" s="20"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="20"/>
-      <c r="N61" s="20"/>
-      <c r="O61" s="21"/>
+      <c r="A61" s="24"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="22"/>
+      <c r="N61" s="22"/>
+      <c r="O61" s="23"/>
     </row>
     <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="22"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="21"/>
+      <c r="A62" s="24"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="22"/>
+      <c r="N62" s="22"/>
+      <c r="O62" s="23"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="22"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="20"/>
-      <c r="O63" s="21"/>
+      <c r="A63" s="24"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="22"/>
+      <c r="N63" s="22"/>
+      <c r="O63" s="23"/>
     </row>
     <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="22"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="20"/>
-      <c r="O64" s="21"/>
+      <c r="A64" s="24"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="23"/>
     </row>
     <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="22"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20"/>
-      <c r="N65" s="20"/>
-      <c r="O65" s="21"/>
+      <c r="A65" s="24"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
+      <c r="O65" s="23"/>
     </row>
     <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="22"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
-      <c r="J66" s="20"/>
-      <c r="K66" s="20"/>
-      <c r="L66" s="20"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="20"/>
-      <c r="O66" s="21"/>
+      <c r="A66" s="24"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="22"/>
+      <c r="K66" s="22"/>
+      <c r="L66" s="22"/>
+      <c r="M66" s="22"/>
+      <c r="N66" s="22"/>
+      <c r="O66" s="23"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="22"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="20"/>
-      <c r="K67" s="20"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="20"/>
-      <c r="N67" s="20"/>
-      <c r="O67" s="21"/>
+      <c r="A67" s="24"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="22"/>
+      <c r="K67" s="22"/>
+      <c r="L67" s="22"/>
+      <c r="M67" s="22"/>
+      <c r="N67" s="22"/>
+      <c r="O67" s="23"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="22"/>
-      <c r="B68" s="23"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
-      <c r="K68" s="20"/>
-      <c r="L68" s="20"/>
-      <c r="M68" s="20"/>
-      <c r="N68" s="20"/>
-      <c r="O68" s="21"/>
+      <c r="A68" s="24"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="23"/>
     </row>
     <row r="69" ht="19.5" customHeight="1">
-      <c r="A69" s="22"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-      <c r="K69" s="20"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="20"/>
-      <c r="N69" s="20"/>
-      <c r="O69" s="21"/>
+      <c r="A69" s="24"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="23"/>
     </row>
     <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="24"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26"/>
-      <c r="K70" s="26"/>
-      <c r="L70" s="26"/>
-      <c r="M70" s="26"/>
-      <c r="N70" s="26"/>
-      <c r="O70" s="27"/>
+      <c r="A70" s="26"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="74">
   <si>
     <t>Table 1</t>
   </si>
@@ -94,6 +94,9 @@
     <t>addiu</t>
   </si>
   <si>
+    <t>`EXT_ZERO</t>
+  </si>
+  <si>
     <t>addu</t>
   </si>
   <si>
@@ -109,9 +112,6 @@
     <t>c</t>
   </si>
   <si>
-    <t>`EXT_ZERO</t>
-  </si>
-  <si>
     <t>beq</t>
   </si>
   <si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>jr</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>`SpecialOP_JR</t>
@@ -1954,7 +1957,7 @@
         <v>25</v>
       </c>
       <c r="M5" t="s" s="16">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N5" t="s" s="16">
         <v>21</v>
@@ -1965,7 +1968,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" t="s" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="15">
         <v>0</v>
@@ -2012,7 +2015,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" t="s" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="15">
         <v>0</v>
@@ -2051,7 +2054,7 @@
         <v>20</v>
       </c>
       <c r="N7" t="s" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O7" t="s" s="13">
         <v>22</v>
@@ -2059,10 +2062,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" t="s" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="16">
         <v>17</v>
@@ -2095,10 +2098,10 @@
         <v>25</v>
       </c>
       <c r="M8" t="s" s="16">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N8" t="s" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O8" t="s" s="13">
         <v>22</v>
@@ -2311,21 +2314,37 @@
       <c r="F13" s="17">
         <v>1</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="11"/>
+      <c r="G13" t="s" s="16">
+        <v>42</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s" s="11">
+        <v>39</v>
+      </c>
       <c r="O13" t="s" s="13">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" t="s" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="15">
         <v>24</v>
@@ -2352,7 +2371,7 @@
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="s" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="15">
         <v>25</v>
@@ -2379,7 +2398,7 @@
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" t="s" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="15">
         <v>30</v>
@@ -2406,10 +2425,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="s" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s" s="18">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s" s="16">
         <v>17</v>
@@ -2433,7 +2452,7 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="s" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="15">
         <v>23</v>
@@ -2460,7 +2479,7 @@
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="15">
         <v>0</v>
@@ -2499,13 +2518,13 @@
         <v>20</v>
       </c>
       <c r="N19" t="s" s="16">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O19" s="13"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="15">
         <v>0</v>
@@ -2544,16 +2563,16 @@
         <v>20</v>
       </c>
       <c r="N20" t="s" s="16">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O20" s="13"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s" s="18">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s" s="16">
         <v>17</v>
@@ -2586,16 +2605,16 @@
         <v>25</v>
       </c>
       <c r="M21" t="s" s="16">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N21" t="s" s="16">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O21" s="13"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="15">
         <v>0</v>
@@ -2607,7 +2626,7 @@
         <v>17</v>
       </c>
       <c r="E22" t="s" s="16">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
@@ -2622,10 +2641,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s" s="18">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s" s="16">
         <v>17</v>
@@ -2649,10 +2668,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s" s="18">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s" s="16">
         <v>17</v>
@@ -2676,7 +2695,7 @@
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>
@@ -2688,7 +2707,7 @@
         <v>17</v>
       </c>
       <c r="E25" t="s" s="16">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
@@ -2703,7 +2722,7 @@
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="15">
         <v>0</v>
@@ -2742,13 +2761,13 @@
         <v>20</v>
       </c>
       <c r="N26" t="s" s="16">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O26" s="13"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="15">
         <v>0</v>
@@ -2787,13 +2806,13 @@
         <v>20</v>
       </c>
       <c r="N27" t="s" s="16">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O27" s="13"/>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="15">
         <v>28</v>
@@ -2820,7 +2839,7 @@
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="15">
         <v>38</v>
@@ -2847,7 +2866,7 @@
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" s="15">
         <v>29</v>
@@ -2874,10 +2893,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s" s="18">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s" s="16">
         <v>17</v>
@@ -2901,7 +2920,7 @@
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" t="s" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" s="15">
         <v>0</v>
@@ -2946,7 +2965,7 @@
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" t="s" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" s="15">
         <v>0</v>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -2358,16 +2358,36 @@
       <c r="E14" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="23"/>
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17">
+        <v>1</v>
+      </c>
+      <c r="J14" s="17">
+        <v>0</v>
+      </c>
+      <c r="K14" s="17">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N14" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O14" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="s" s="14">
@@ -2826,15 +2846,33 @@
       <c r="E28" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="F28" s="19">
+        <v>0</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19">
+        <v>1</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M28" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N28" t="s" s="16">
+        <v>21</v>
+      </c>
       <c r="O28" s="23"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
@@ -2907,16 +2945,36 @@
       <c r="E31" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="23"/>
+      <c r="F31" s="19">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s" s="16">
+        <v>42</v>
+      </c>
+      <c r="H31" s="19">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19">
+        <v>0</v>
+      </c>
+      <c r="J31" s="19">
+        <v>1</v>
+      </c>
+      <c r="K31" s="19">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M31" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N31" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" t="s" s="14">

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
   <si>
     <t>Table 1</t>
   </si>
@@ -220,10 +220,16 @@
     <t>sb</t>
   </si>
   <si>
+    <t>`SpecialOP_DM_BYTE</t>
+  </si>
+  <si>
     <t>sc</t>
   </si>
   <si>
     <t>sh</t>
+  </si>
+  <si>
+    <t>`SpecialOP_DM_HW</t>
   </si>
   <si>
     <t>sw</t>
@@ -2849,8 +2855,8 @@
       <c r="F28" s="19">
         <v>0</v>
       </c>
-      <c r="G28" s="19">
-        <v>0</v>
+      <c r="G28" t="s" s="16">
+        <v>42</v>
       </c>
       <c r="H28" s="19">
         <v>0</v>
@@ -2873,11 +2879,13 @@
       <c r="N28" t="s" s="16">
         <v>21</v>
       </c>
-      <c r="O28" s="23"/>
+      <c r="O28" t="s" s="13">
+        <v>69</v>
+      </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" s="15">
         <v>38</v>
@@ -2891,20 +2899,38 @@
       <c r="E29" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="23"/>
+      <c r="F29" s="19">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s" s="16">
+        <v>42</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19">
+        <v>0</v>
+      </c>
+      <c r="J29" s="19">
+        <v>1</v>
+      </c>
+      <c r="K29" s="19">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N29" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O29" s="13"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="15">
         <v>29</v>
@@ -2918,20 +2944,40 @@
       <c r="E30" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="23"/>
+      <c r="F30" s="19">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s" s="16">
+        <v>42</v>
+      </c>
+      <c r="H30" s="19">
+        <v>0</v>
+      </c>
+      <c r="I30" s="19">
+        <v>0</v>
+      </c>
+      <c r="J30" s="19">
+        <v>1</v>
+      </c>
+      <c r="K30" s="19">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N30" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s" s="13">
+        <v>72</v>
+      </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s" s="18">
         <v>63</v>
@@ -2978,7 +3024,7 @@
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" t="s" s="14">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B32" s="15">
         <v>0</v>
@@ -3023,7 +3069,7 @@
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" t="s" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B33" s="15">
         <v>0</v>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -148,9 +148,15 @@
     <t>lbu</t>
   </si>
   <si>
+    <t>`SpecialOP_DM_BYTE</t>
+  </si>
+  <si>
     <t>lhu</t>
   </si>
   <si>
+    <t>`SpecialOP_DM_HW</t>
+  </si>
+  <si>
     <t>ll</t>
   </si>
   <si>
@@ -220,16 +226,10 @@
     <t>sb</t>
   </si>
   <si>
-    <t>`SpecialOP_DM_BYTE</t>
-  </si>
-  <si>
     <t>sc</t>
   </si>
   <si>
     <t>sh</t>
-  </si>
-  <si>
-    <t>`SpecialOP_DM_HW</t>
   </si>
   <si>
     <t>sw</t>
@@ -2392,12 +2392,12 @@
         <v>21</v>
       </c>
       <c r="O14" t="s" s="13">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="s" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="15">
         <v>25</v>
@@ -2411,20 +2411,40 @@
       <c r="E15" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="23"/>
+      <c r="F15" s="17">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17">
+        <v>1</v>
+      </c>
+      <c r="J15" s="17">
+        <v>0</v>
+      </c>
+      <c r="K15" s="17">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N15" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s" s="13">
+        <v>47</v>
+      </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" t="s" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16" s="15">
         <v>30</v>
@@ -2438,23 +2458,43 @@
       <c r="E16" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="23"/>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>1</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N16" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="s" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s" s="18">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s" s="16">
         <v>17</v>
@@ -2478,7 +2518,7 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="s" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="15">
         <v>23</v>
@@ -2492,20 +2532,40 @@
       <c r="E18" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="23"/>
+      <c r="F18" s="17">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0</v>
+      </c>
+      <c r="I18" s="17">
+        <v>1</v>
+      </c>
+      <c r="J18" s="17">
+        <v>0</v>
+      </c>
+      <c r="K18" s="17">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M18" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N18" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O18" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" s="15">
         <v>0</v>
@@ -2544,13 +2604,13 @@
         <v>20</v>
       </c>
       <c r="N19" t="s" s="16">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O19" s="13"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B20" s="15">
         <v>0</v>
@@ -2589,16 +2649,16 @@
         <v>20</v>
       </c>
       <c r="N20" t="s" s="16">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O20" s="13"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s" s="18">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s" s="16">
         <v>17</v>
@@ -2634,13 +2694,13 @@
         <v>27</v>
       </c>
       <c r="N21" t="s" s="16">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O21" s="13"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="15">
         <v>0</v>
@@ -2652,7 +2712,7 @@
         <v>17</v>
       </c>
       <c r="E22" t="s" s="16">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
@@ -2667,10 +2727,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s" s="18">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s" s="16">
         <v>17</v>
@@ -2694,10 +2754,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s" s="18">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s" s="16">
         <v>17</v>
@@ -2721,7 +2781,7 @@
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>
@@ -2733,7 +2793,7 @@
         <v>17</v>
       </c>
       <c r="E25" t="s" s="16">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
@@ -2748,7 +2808,7 @@
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B26" s="15">
         <v>0</v>
@@ -2787,13 +2847,13 @@
         <v>20</v>
       </c>
       <c r="N26" t="s" s="16">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O26" s="13"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="14">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B27" s="15">
         <v>0</v>
@@ -2832,13 +2892,13 @@
         <v>20</v>
       </c>
       <c r="N27" t="s" s="16">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O27" s="13"/>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B28" s="15">
         <v>28</v>
@@ -2880,12 +2940,12 @@
         <v>21</v>
       </c>
       <c r="O28" t="s" s="13">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="15">
         <v>38</v>
@@ -2930,7 +2990,7 @@
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" s="15">
         <v>29</v>
@@ -2972,7 +3032,7 @@
         <v>21</v>
       </c>
       <c r="O30" t="s" s="13">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
@@ -2980,7 +3040,7 @@
         <v>73</v>
       </c>
       <c r="B31" t="s" s="18">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s" s="16">
         <v>17</v>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="74">
   <si>
     <t>Table 1</t>
   </si>
@@ -157,9 +157,6 @@
     <t>`SpecialOP_DM_HW</t>
   </si>
   <si>
-    <t>ll</t>
-  </si>
-  <si>
     <t>lui</t>
   </si>
   <si>
@@ -224,9 +221,6 @@
   </si>
   <si>
     <t>sb</t>
-  </si>
-  <si>
-    <t>sc</t>
   </si>
   <si>
     <t>sh</t>
@@ -1758,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
@@ -2446,8 +2440,8 @@
       <c r="A16" t="s" s="14">
         <v>48</v>
       </c>
-      <c r="B16" s="15">
-        <v>30</v>
+      <c r="B16" t="s" s="18">
+        <v>49</v>
       </c>
       <c r="C16" t="s" s="16">
         <v>17</v>
@@ -2458,44 +2452,24 @@
       <c r="E16" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F16" s="17">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s" s="16">
-        <v>24</v>
-      </c>
-      <c r="H16" s="17">
-        <v>0</v>
-      </c>
-      <c r="I16" s="17">
-        <v>1</v>
-      </c>
-      <c r="J16" s="17">
-        <v>0</v>
-      </c>
-      <c r="K16" s="17">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s" s="16">
-        <v>25</v>
-      </c>
-      <c r="M16" t="s" s="16">
-        <v>20</v>
-      </c>
-      <c r="N16" t="s" s="16">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s" s="13">
-        <v>22</v>
-      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="23"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="s" s="14">
-        <v>49</v>
-      </c>
-      <c r="B17" t="s" s="18">
         <v>50</v>
       </c>
+      <c r="B17" s="15">
+        <v>23</v>
+      </c>
       <c r="C17" t="s" s="16">
         <v>17</v>
       </c>
@@ -2505,23 +2479,43 @@
       <c r="E17" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="23"/>
+      <c r="F17" s="17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="17">
+        <v>1</v>
+      </c>
+      <c r="J17" s="17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N17" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O17" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="s" s="14">
         <v>51</v>
       </c>
       <c r="B18" s="15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C18" t="s" s="16">
         <v>17</v>
@@ -2529,20 +2523,20 @@
       <c r="D18" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="E18" t="s" s="16">
-        <v>17</v>
+      <c r="E18" s="17">
+        <v>27</v>
       </c>
       <c r="F18" s="17">
         <v>0</v>
       </c>
       <c r="G18" t="s" s="16">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H18" s="17">
         <v>0</v>
       </c>
       <c r="I18" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="17">
         <v>0</v>
@@ -2551,21 +2545,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="s" s="16">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M18" t="s" s="16">
         <v>20</v>
       </c>
       <c r="N18" t="s" s="16">
-        <v>21</v>
-      </c>
-      <c r="O18" t="s" s="13">
-        <v>22</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="O18" s="13"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="15">
         <v>0</v>
@@ -2577,7 +2569,7 @@
         <v>17</v>
       </c>
       <c r="E19" s="17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="17">
         <v>0</v>
@@ -2604,16 +2596,16 @@
         <v>20</v>
       </c>
       <c r="N19" t="s" s="16">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O19" s="13"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="14">
-        <v>54</v>
-      </c>
-      <c r="B20" s="15">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="B20" t="s" s="18">
+        <v>56</v>
       </c>
       <c r="C20" t="s" s="16">
         <v>17</v>
@@ -2621,14 +2613,14 @@
       <c r="D20" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="E20" s="17">
-        <v>25</v>
+      <c r="E20" t="s" s="16">
+        <v>17</v>
       </c>
       <c r="F20" s="17">
         <v>0</v>
       </c>
       <c r="G20" t="s" s="16">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H20" s="17">
         <v>0</v>
@@ -2643,23 +2635,23 @@
         <v>1</v>
       </c>
       <c r="L20" t="s" s="16">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M20" t="s" s="16">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N20" t="s" s="16">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O20" s="13"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="14">
-        <v>56</v>
-      </c>
-      <c r="B21" t="s" s="18">
         <v>57</v>
       </c>
+      <c r="B21" s="15">
+        <v>0</v>
+      </c>
       <c r="C21" t="s" s="16">
         <v>17</v>
       </c>
@@ -2667,43 +2659,25 @@
         <v>17</v>
       </c>
       <c r="E21" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="F21" s="17">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s" s="16">
-        <v>24</v>
-      </c>
-      <c r="H21" s="17">
-        <v>0</v>
-      </c>
-      <c r="I21" s="17">
-        <v>0</v>
-      </c>
-      <c r="J21" s="17">
-        <v>0</v>
-      </c>
-      <c r="K21" s="17">
-        <v>1</v>
-      </c>
-      <c r="L21" t="s" s="16">
-        <v>25</v>
-      </c>
-      <c r="M21" t="s" s="16">
-        <v>27</v>
-      </c>
-      <c r="N21" t="s" s="16">
-        <v>55</v>
-      </c>
-      <c r="O21" s="13"/>
+        <v>58</v>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="23"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="14">
-        <v>58</v>
-      </c>
-      <c r="B22" s="15">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="B22" t="s" s="18">
+        <v>60</v>
       </c>
       <c r="C22" t="s" s="16">
         <v>17</v>
@@ -2712,7 +2686,7 @@
         <v>17</v>
       </c>
       <c r="E22" t="s" s="16">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
@@ -2727,10 +2701,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s" s="18">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s" s="16">
         <v>17</v>
@@ -2754,11 +2728,11 @@
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="14">
-        <v>62</v>
-      </c>
-      <c r="B24" t="s" s="18">
         <v>63</v>
       </c>
+      <c r="B24" s="15">
+        <v>0</v>
+      </c>
       <c r="C24" t="s" s="16">
         <v>17</v>
       </c>
@@ -2766,7 +2740,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="s" s="16">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -2781,7 +2755,7 @@
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>
@@ -2792,23 +2766,41 @@
       <c r="D25" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="E25" t="s" s="16">
-        <v>65</v>
-      </c>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="23"/>
+      <c r="E25" s="17">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s" s="16">
+        <v>18</v>
+      </c>
+      <c r="H25" s="17">
+        <v>0</v>
+      </c>
+      <c r="I25" s="17">
+        <v>0</v>
+      </c>
+      <c r="J25" s="17">
+        <v>0</v>
+      </c>
+      <c r="K25" s="17">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M25" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N25" t="s" s="16">
+        <v>66</v>
+      </c>
+      <c r="O25" s="13"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="15">
         <v>0</v>
@@ -2820,7 +2812,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="17">
         <v>0</v>
@@ -2847,16 +2839,16 @@
         <v>20</v>
       </c>
       <c r="N26" t="s" s="16">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O26" s="13"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B27" s="15">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s" s="16">
         <v>17</v>
@@ -2864,44 +2856,46 @@
       <c r="D27" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="E27" s="17">
-        <v>2</v>
-      </c>
-      <c r="F27" s="17">
+      <c r="E27" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="F27" s="19">
         <v>0</v>
       </c>
       <c r="G27" t="s" s="16">
-        <v>18</v>
-      </c>
-      <c r="H27" s="17">
-        <v>0</v>
-      </c>
-      <c r="I27" s="17">
-        <v>0</v>
-      </c>
-      <c r="J27" s="17">
-        <v>0</v>
-      </c>
-      <c r="K27" s="17">
+        <v>42</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19">
         <v>1</v>
       </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
       <c r="L27" t="s" s="16">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M27" t="s" s="16">
         <v>20</v>
       </c>
       <c r="N27" t="s" s="16">
-        <v>69</v>
-      </c>
-      <c r="O27" s="13"/>
+        <v>21</v>
+      </c>
+      <c r="O27" t="s" s="13">
+        <v>45</v>
+      </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="14">
         <v>70</v>
       </c>
       <c r="B28" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s" s="16">
         <v>17</v>
@@ -2940,15 +2934,15 @@
         <v>21</v>
       </c>
       <c r="O28" t="s" s="13">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
         <v>71</v>
       </c>
-      <c r="B29" s="15">
-        <v>38</v>
+      <c r="B29" t="s" s="18">
+        <v>64</v>
       </c>
       <c r="C29" t="s" s="16">
         <v>17</v>
@@ -2986,14 +2980,16 @@
       <c r="N29" t="s" s="16">
         <v>21</v>
       </c>
-      <c r="O29" s="13"/>
+      <c r="O29" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
         <v>72</v>
       </c>
       <c r="B30" s="15">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C30" t="s" s="16">
         <v>17</v>
@@ -3001,46 +2997,44 @@
       <c r="D30" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="E30" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="F30" s="19">
+      <c r="E30" s="17">
+        <v>22</v>
+      </c>
+      <c r="F30" s="17">
         <v>0</v>
       </c>
       <c r="G30" t="s" s="16">
-        <v>42</v>
-      </c>
-      <c r="H30" s="19">
-        <v>0</v>
-      </c>
-      <c r="I30" s="19">
-        <v>0</v>
-      </c>
-      <c r="J30" s="19">
+        <v>18</v>
+      </c>
+      <c r="H30" s="17">
+        <v>0</v>
+      </c>
+      <c r="I30" s="17">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17">
+        <v>0</v>
+      </c>
+      <c r="K30" s="17">
         <v>1</v>
       </c>
-      <c r="K30" s="19">
-        <v>0</v>
-      </c>
       <c r="L30" t="s" s="16">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M30" t="s" s="16">
         <v>20</v>
       </c>
       <c r="N30" t="s" s="16">
-        <v>21</v>
-      </c>
-      <c r="O30" t="s" s="13">
-        <v>47</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="O30" s="13"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="14">
         <v>73</v>
       </c>
-      <c r="B31" t="s" s="18">
-        <v>65</v>
+      <c r="B31" s="15">
+        <v>0</v>
       </c>
       <c r="C31" t="s" s="16">
         <v>17</v>
@@ -3048,129 +3042,71 @@
       <c r="D31" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="E31" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="F31" s="19">
+      <c r="E31" s="17">
+        <v>23</v>
+      </c>
+      <c r="F31" s="17">
         <v>0</v>
       </c>
       <c r="G31" t="s" s="16">
-        <v>42</v>
-      </c>
-      <c r="H31" s="19">
-        <v>0</v>
-      </c>
-      <c r="I31" s="19">
-        <v>0</v>
-      </c>
-      <c r="J31" s="19">
+        <v>18</v>
+      </c>
+      <c r="H31" s="17">
+        <v>0</v>
+      </c>
+      <c r="I31" s="17">
+        <v>0</v>
+      </c>
+      <c r="J31" s="17">
+        <v>0</v>
+      </c>
+      <c r="K31" s="17">
         <v>1</v>
       </c>
-      <c r="K31" s="19">
-        <v>0</v>
-      </c>
       <c r="L31" t="s" s="16">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M31" t="s" s="16">
         <v>20</v>
       </c>
       <c r="N31" t="s" s="16">
-        <v>21</v>
-      </c>
-      <c r="O31" t="s" s="13">
-        <v>22</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="O31" s="13"/>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" t="s" s="14">
-        <v>74</v>
-      </c>
-      <c r="B32" s="15">
-        <v>0</v>
-      </c>
-      <c r="C32" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="D32" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="E32" s="17">
-        <v>22</v>
-      </c>
-      <c r="F32" s="17">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s" s="16">
-        <v>18</v>
-      </c>
-      <c r="H32" s="17">
-        <v>0</v>
-      </c>
-      <c r="I32" s="17">
-        <v>0</v>
-      </c>
-      <c r="J32" s="17">
-        <v>0</v>
-      </c>
-      <c r="K32" s="17">
-        <v>1</v>
-      </c>
-      <c r="L32" t="s" s="16">
-        <v>19</v>
-      </c>
-      <c r="M32" t="s" s="16">
-        <v>20</v>
-      </c>
-      <c r="N32" t="s" s="16">
-        <v>34</v>
-      </c>
-      <c r="O32" s="13"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="23"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" t="s" s="14">
-        <v>75</v>
-      </c>
-      <c r="B33" s="15">
-        <v>0</v>
-      </c>
-      <c r="C33" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="D33" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="E33" s="17">
-        <v>23</v>
-      </c>
-      <c r="F33" s="17">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s" s="16">
-        <v>18</v>
-      </c>
-      <c r="H33" s="17">
-        <v>0</v>
-      </c>
-      <c r="I33" s="17">
-        <v>0</v>
-      </c>
-      <c r="J33" s="17">
-        <v>0</v>
-      </c>
-      <c r="K33" s="17">
-        <v>1</v>
-      </c>
-      <c r="L33" t="s" s="16">
-        <v>19</v>
-      </c>
-      <c r="M33" t="s" s="16">
-        <v>20</v>
-      </c>
-      <c r="N33" t="s" s="16">
-        <v>34</v>
-      </c>
-      <c r="O33" s="13"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="23"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="24"/>
@@ -3751,55 +3687,21 @@
       <c r="O67" s="23"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="24"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-      <c r="L68" s="22"/>
-      <c r="M68" s="22"/>
-      <c r="N68" s="22"/>
-      <c r="O68" s="23"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="A69" s="24"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="22"/>
-      <c r="L69" s="22"/>
-      <c r="M69" s="22"/>
-      <c r="N69" s="22"/>
-      <c r="O69" s="23"/>
-    </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="26"/>
-      <c r="B70" s="27"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="29"/>
+      <c r="A68" s="26"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="28"/>
+      <c r="K68" s="28"/>
+      <c r="L68" s="28"/>
+      <c r="M68" s="28"/>
+      <c r="N68" s="28"/>
+      <c r="O68" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
   <si>
     <t>Table 1</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>f</t>
+  </si>
+  <si>
+    <t>`ALUOp_LUI</t>
   </si>
   <si>
     <t>lw</t>
@@ -2452,20 +2455,40 @@
       <c r="E16" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="23"/>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s" s="16">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s" s="16">
+        <v>50</v>
+      </c>
+      <c r="O16" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="s" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="15">
         <v>23</v>
@@ -2512,7 +2535,7 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="s" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="15">
         <v>0</v>
@@ -2551,13 +2574,13 @@
         <v>20</v>
       </c>
       <c r="N18" t="s" s="16">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O18" s="13"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="15">
         <v>0</v>
@@ -2596,16 +2619,16 @@
         <v>20</v>
       </c>
       <c r="N19" t="s" s="16">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O19" s="13"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s" s="18">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s" s="16">
         <v>17</v>
@@ -2641,13 +2664,13 @@
         <v>27</v>
       </c>
       <c r="N20" t="s" s="16">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O20" s="13"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="15">
         <v>0</v>
@@ -2659,7 +2682,7 @@
         <v>17</v>
       </c>
       <c r="E21" t="s" s="16">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
@@ -2674,10 +2697,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s" s="18">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s" s="16">
         <v>17</v>
@@ -2701,10 +2724,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s" s="18">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s" s="16">
         <v>17</v>
@@ -2728,7 +2751,7 @@
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="15">
         <v>0</v>
@@ -2740,7 +2763,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="s" s="16">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -2755,7 +2778,7 @@
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>
@@ -2794,13 +2817,13 @@
         <v>20</v>
       </c>
       <c r="N25" t="s" s="16">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O25" s="13"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="15">
         <v>0</v>
@@ -2839,13 +2862,13 @@
         <v>20</v>
       </c>
       <c r="N26" t="s" s="16">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O26" s="13"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="15">
         <v>28</v>
@@ -2892,7 +2915,7 @@
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="15">
         <v>29</v>
@@ -2939,10 +2962,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s" s="18">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s" s="16">
         <v>17</v>
@@ -2986,7 +3009,7 @@
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="15">
         <v>0</v>
@@ -3031,7 +3054,7 @@
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="14">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" s="15">
         <v>0</v>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="s" s="16">
         <v>25</v>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
   <si>
     <t>Table 1</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>2a</t>
+  </si>
+  <si>
+    <t>`ALUOp_SLT</t>
   </si>
   <si>
     <t>slti</t>
@@ -677,16 +680,16 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -2576,7 +2579,9 @@
       <c r="N18" t="s" s="16">
         <v>53</v>
       </c>
-      <c r="O18" s="13"/>
+      <c r="O18" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="14">
@@ -2621,7 +2626,9 @@
       <c r="N19" t="s" s="16">
         <v>55</v>
       </c>
-      <c r="O19" s="13"/>
+      <c r="O19" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="14">
@@ -2666,7 +2673,9 @@
       <c r="N20" t="s" s="16">
         <v>55</v>
       </c>
-      <c r="O20" s="13"/>
+      <c r="O20" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="14">
@@ -2684,50 +2693,90 @@
       <c r="E21" t="s" s="16">
         <v>59</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="23"/>
+      <c r="F21" s="17">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s" s="16">
+        <v>18</v>
+      </c>
+      <c r="H21" s="17">
+        <v>0</v>
+      </c>
+      <c r="I21" s="17">
+        <v>0</v>
+      </c>
+      <c r="J21" s="17">
+        <v>0</v>
+      </c>
+      <c r="K21" s="17">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M21" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N21" t="s" s="16">
+        <v>60</v>
+      </c>
+      <c r="O21" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="14">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s" s="18">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="F22" s="17">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H22" s="17">
+        <v>0</v>
+      </c>
+      <c r="I22" s="17">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17">
+        <v>0</v>
+      </c>
+      <c r="K22" s="17">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N22" t="s" s="16">
         <v>60</v>
       </c>
-      <c r="B22" t="s" s="18">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="E22" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="23"/>
+      <c r="O22" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s" s="18">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="16">
         <v>17</v>
@@ -2738,20 +2787,40 @@
       <c r="E23" t="s" s="16">
         <v>17</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="23"/>
+      <c r="F23" s="17">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0</v>
+      </c>
+      <c r="I23" s="17">
+        <v>0</v>
+      </c>
+      <c r="J23" s="17">
+        <v>0</v>
+      </c>
+      <c r="K23" s="17">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s" s="16">
+        <v>27</v>
+      </c>
+      <c r="N23" t="s" s="16">
+        <v>60</v>
+      </c>
+      <c r="O23" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" s="15">
         <v>0</v>
@@ -2763,22 +2832,42 @@
         <v>17</v>
       </c>
       <c r="E24" t="s" s="16">
-        <v>65</v>
-      </c>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="23"/>
+        <v>66</v>
+      </c>
+      <c r="F24" s="17">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s" s="16">
+        <v>18</v>
+      </c>
+      <c r="H24" s="17">
+        <v>0</v>
+      </c>
+      <c r="I24" s="17">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17">
+        <v>0</v>
+      </c>
+      <c r="K24" s="17">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M24" t="s" s="16">
+        <v>27</v>
+      </c>
+      <c r="N24" t="s" s="16">
+        <v>60</v>
+      </c>
+      <c r="O24" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>
@@ -2817,13 +2906,15 @@
         <v>20</v>
       </c>
       <c r="N25" t="s" s="16">
-        <v>67</v>
-      </c>
-      <c r="O25" s="13"/>
+        <v>68</v>
+      </c>
+      <c r="O25" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="15">
         <v>0</v>
@@ -2862,13 +2953,15 @@
         <v>20</v>
       </c>
       <c r="N26" t="s" s="16">
-        <v>69</v>
-      </c>
-      <c r="O26" s="13"/>
+        <v>70</v>
+      </c>
+      <c r="O26" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="15">
         <v>28</v>
@@ -2915,7 +3008,7 @@
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="15">
         <v>29</v>
@@ -2962,10 +3055,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s" s="18">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s" s="16">
         <v>17</v>
@@ -3009,7 +3102,7 @@
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="15">
         <v>0</v>
@@ -3050,11 +3143,13 @@
       <c r="N30" t="s" s="16">
         <v>34</v>
       </c>
-      <c r="O30" s="13"/>
+      <c r="O30" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="14">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="15">
         <v>0</v>
@@ -3095,619 +3190,621 @@
       <c r="N31" t="s" s="16">
         <v>34</v>
       </c>
-      <c r="O31" s="13"/>
+      <c r="O31" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="24"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="23"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="25"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="24"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="23"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="25"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="23"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="25"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="23"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="25"/>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="24"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="23"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="24"/>
+      <c r="O36" s="25"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="24"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="23"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="25"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="24"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="23"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="25"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="24"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="23"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="25"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="23"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="25"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="22"/>
-      <c r="O41" s="23"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="25"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="24"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="23"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="25"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="24"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="22"/>
-      <c r="O43" s="23"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="24"/>
+      <c r="N43" s="24"/>
+      <c r="O43" s="25"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="24"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="23"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="24"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="24"/>
+      <c r="N44" s="24"/>
+      <c r="O44" s="25"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="24"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="22"/>
-      <c r="O45" s="23"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="24"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="24"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="25"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="24"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="23"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="24"/>
+      <c r="N46" s="24"/>
+      <c r="O46" s="25"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="24"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="23"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="24"/>
+      <c r="N47" s="24"/>
+      <c r="O47" s="25"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="24"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="22"/>
-      <c r="O48" s="23"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="24"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="25"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="24"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="22"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="22"/>
-      <c r="N49" s="22"/>
-      <c r="O49" s="23"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24"/>
+      <c r="N49" s="24"/>
+      <c r="O49" s="25"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="24"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="22"/>
-      <c r="L50" s="22"/>
-      <c r="M50" s="22"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="23"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="24"/>
+      <c r="N50" s="24"/>
+      <c r="O50" s="25"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="24"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22"/>
-      <c r="J51" s="22"/>
-      <c r="K51" s="22"/>
-      <c r="L51" s="22"/>
-      <c r="M51" s="22"/>
-      <c r="N51" s="22"/>
-      <c r="O51" s="23"/>
+      <c r="A51" s="22"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+      <c r="N51" s="24"/>
+      <c r="O51" s="25"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="24"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="22"/>
-      <c r="N52" s="22"/>
-      <c r="O52" s="23"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="24"/>
+      <c r="O52" s="25"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="24"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="22"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="22"/>
-      <c r="O53" s="23"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="24"/>
+      <c r="N53" s="24"/>
+      <c r="O53" s="25"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="24"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
-      <c r="O54" s="23"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="24"/>
+      <c r="N54" s="24"/>
+      <c r="O54" s="25"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="24"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="22"/>
-      <c r="N55" s="22"/>
-      <c r="O55" s="23"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="24"/>
+      <c r="N55" s="24"/>
+      <c r="O55" s="25"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="24"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="22"/>
-      <c r="L56" s="22"/>
-      <c r="M56" s="22"/>
-      <c r="N56" s="22"/>
-      <c r="O56" s="23"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="24"/>
+      <c r="N56" s="24"/>
+      <c r="O56" s="25"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="24"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="22"/>
-      <c r="L57" s="22"/>
-      <c r="M57" s="22"/>
-      <c r="N57" s="22"/>
-      <c r="O57" s="23"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="24"/>
+      <c r="N57" s="24"/>
+      <c r="O57" s="25"/>
     </row>
     <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="24"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="22"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="23"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="24"/>
+      <c r="L58" s="24"/>
+      <c r="M58" s="24"/>
+      <c r="N58" s="24"/>
+      <c r="O58" s="25"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="24"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="22"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="23"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="24"/>
+      <c r="K59" s="24"/>
+      <c r="L59" s="24"/>
+      <c r="M59" s="24"/>
+      <c r="N59" s="24"/>
+      <c r="O59" s="25"/>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="24"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="22"/>
-      <c r="N60" s="22"/>
-      <c r="O60" s="23"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="24"/>
+      <c r="J60" s="24"/>
+      <c r="K60" s="24"/>
+      <c r="L60" s="24"/>
+      <c r="M60" s="24"/>
+      <c r="N60" s="24"/>
+      <c r="O60" s="25"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="24"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="23"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="25"/>
     </row>
     <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="24"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="23"/>
+      <c r="A62" s="22"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="24"/>
+      <c r="K62" s="24"/>
+      <c r="L62" s="24"/>
+      <c r="M62" s="24"/>
+      <c r="N62" s="24"/>
+      <c r="O62" s="25"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="24"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="23"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="24"/>
+      <c r="K63" s="24"/>
+      <c r="L63" s="24"/>
+      <c r="M63" s="24"/>
+      <c r="N63" s="24"/>
+      <c r="O63" s="25"/>
     </row>
     <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="24"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-      <c r="J64" s="22"/>
-      <c r="K64" s="22"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="22"/>
-      <c r="N64" s="22"/>
-      <c r="O64" s="23"/>
+      <c r="A64" s="22"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="24"/>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="24"/>
+      <c r="N64" s="24"/>
+      <c r="O64" s="25"/>
     </row>
     <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="24"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="22"/>
-      <c r="N65" s="22"/>
-      <c r="O65" s="23"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
+      <c r="J65" s="24"/>
+      <c r="K65" s="24"/>
+      <c r="L65" s="24"/>
+      <c r="M65" s="24"/>
+      <c r="N65" s="24"/>
+      <c r="O65" s="25"/>
     </row>
     <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="24"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="22"/>
-      <c r="K66" s="22"/>
-      <c r="L66" s="22"/>
-      <c r="M66" s="22"/>
-      <c r="N66" s="22"/>
-      <c r="O66" s="23"/>
+      <c r="A66" s="22"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="J66" s="24"/>
+      <c r="K66" s="24"/>
+      <c r="L66" s="24"/>
+      <c r="M66" s="24"/>
+      <c r="N66" s="24"/>
+      <c r="O66" s="25"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="24"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="22"/>
-      <c r="K67" s="22"/>
-      <c r="L67" s="22"/>
-      <c r="M67" s="22"/>
-      <c r="N67" s="22"/>
-      <c r="O67" s="23"/>
+      <c r="A67" s="22"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="24"/>
+      <c r="K67" s="24"/>
+      <c r="L67" s="24"/>
+      <c r="M67" s="24"/>
+      <c r="N67" s="24"/>
+      <c r="O67" s="25"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
       <c r="A68" s="26"/>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
   <si>
     <t>Table 1</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>subu</t>
+  </si>
+  <si>
+    <t>lb</t>
   </si>
 </sst>
 </file>
@@ -3195,21 +3198,51 @@
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="25"/>
+      <c r="A32" t="s" s="14">
+        <v>76</v>
+      </c>
+      <c r="B32" s="15">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="F32" s="17">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s" s="16">
+        <v>24</v>
+      </c>
+      <c r="H32" s="17">
+        <v>0</v>
+      </c>
+      <c r="I32" s="17">
+        <v>1</v>
+      </c>
+      <c r="J32" s="17">
+        <v>0</v>
+      </c>
+      <c r="K32" s="17">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s" s="16">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N32" t="s" s="16">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s" s="13">
+        <v>45</v>
+      </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="22"/>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
   <si>
     <t>Table 1</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>lb</t>
+  </si>
+  <si>
+    <t>sra</t>
+  </si>
+  <si>
+    <t>`ALUOp_SRA</t>
   </si>
 </sst>
 </file>
@@ -3245,21 +3251,51 @@
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="22"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="25"/>
+      <c r="A33" t="s" s="14">
+        <v>77</v>
+      </c>
+      <c r="B33" s="15">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3</v>
+      </c>
+      <c r="F33" s="17">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s" s="16">
+        <v>18</v>
+      </c>
+      <c r="H33" s="17">
+        <v>0</v>
+      </c>
+      <c r="I33" s="17">
+        <v>0</v>
+      </c>
+      <c r="J33" s="17">
+        <v>0</v>
+      </c>
+      <c r="K33" s="17">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M33" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N33" t="s" s="16">
+        <v>78</v>
+      </c>
+      <c r="O33" t="s" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="22"/>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="80">
   <si>
     <t>Table 1</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>`ALUOp_SRA</t>
+  </si>
+  <si>
+    <t>nop</t>
   </si>
 </sst>
 </file>
@@ -622,7 +625,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -687,6 +690,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -3298,599 +3304,629 @@
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="22"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="25"/>
+      <c r="A34" t="s" s="14">
+        <v>79</v>
+      </c>
+      <c r="B34" s="15">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0</v>
+      </c>
+      <c r="H34" s="17">
+        <v>0</v>
+      </c>
+      <c r="I34" s="17">
+        <v>0</v>
+      </c>
+      <c r="J34" s="17">
+        <v>0</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
+      <c r="L34" s="17">
+        <v>0</v>
+      </c>
+      <c r="M34" s="17">
+        <v>0</v>
+      </c>
+      <c r="N34" s="17">
+        <v>0</v>
+      </c>
+      <c r="O34" s="22">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="25"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="26"/>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="22"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="25"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="26"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="25"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="26"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="22"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="25"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="26"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="22"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="25"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="26"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="22"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="25"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="26"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="22"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="25"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="26"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="22"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="25"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="26"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="22"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="24"/>
-      <c r="N43" s="24"/>
-      <c r="O43" s="25"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="25"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="26"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="22"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="24"/>
-      <c r="N44" s="24"/>
-      <c r="O44" s="25"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="26"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="22"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="24"/>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="24"/>
-      <c r="N45" s="24"/>
-      <c r="O45" s="25"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="25"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="26"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="22"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="24"/>
-      <c r="N46" s="24"/>
-      <c r="O46" s="25"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="25"/>
+      <c r="M46" s="25"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="26"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="22"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="24"/>
-      <c r="N47" s="24"/>
-      <c r="O47" s="25"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="25"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="26"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="22"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="24"/>
-      <c r="N48" s="24"/>
-      <c r="O48" s="25"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="25"/>
+      <c r="M48" s="25"/>
+      <c r="N48" s="25"/>
+      <c r="O48" s="26"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="22"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="24"/>
-      <c r="N49" s="24"/>
-      <c r="O49" s="25"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="25"/>
+      <c r="K49" s="25"/>
+      <c r="L49" s="25"/>
+      <c r="M49" s="25"/>
+      <c r="N49" s="25"/>
+      <c r="O49" s="26"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="22"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="24"/>
-      <c r="N50" s="24"/>
-      <c r="O50" s="25"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="26"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="22"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="24"/>
-      <c r="L51" s="24"/>
-      <c r="M51" s="24"/>
-      <c r="N51" s="24"/>
-      <c r="O51" s="25"/>
+      <c r="A51" s="23"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="25"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="26"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="22"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="24"/>
-      <c r="N52" s="24"/>
-      <c r="O52" s="25"/>
+      <c r="A52" s="23"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="25"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="25"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="26"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="22"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="24"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="24"/>
-      <c r="N53" s="24"/>
-      <c r="O53" s="25"/>
+      <c r="A53" s="23"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="25"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="26"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="22"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="24"/>
-      <c r="L54" s="24"/>
-      <c r="M54" s="24"/>
-      <c r="N54" s="24"/>
-      <c r="O54" s="25"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="25"/>
+      <c r="O54" s="26"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="24"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="24"/>
-      <c r="N55" s="24"/>
-      <c r="O55" s="25"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="26"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="22"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="24"/>
-      <c r="K56" s="24"/>
-      <c r="L56" s="24"/>
-      <c r="M56" s="24"/>
-      <c r="N56" s="24"/>
-      <c r="O56" s="25"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="26"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="24"/>
-      <c r="K57" s="24"/>
-      <c r="L57" s="24"/>
-      <c r="M57" s="24"/>
-      <c r="N57" s="24"/>
-      <c r="O57" s="25"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="25"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="26"/>
     </row>
     <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="24"/>
-      <c r="K58" s="24"/>
-      <c r="L58" s="24"/>
-      <c r="M58" s="24"/>
-      <c r="N58" s="24"/>
-      <c r="O58" s="25"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="25"/>
+      <c r="O58" s="26"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="22"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="24"/>
-      <c r="K59" s="24"/>
-      <c r="L59" s="24"/>
-      <c r="M59" s="24"/>
-      <c r="N59" s="24"/>
-      <c r="O59" s="25"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="25"/>
+      <c r="L59" s="25"/>
+      <c r="M59" s="25"/>
+      <c r="N59" s="25"/>
+      <c r="O59" s="26"/>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="24"/>
-      <c r="K60" s="24"/>
-      <c r="L60" s="24"/>
-      <c r="M60" s="24"/>
-      <c r="N60" s="24"/>
-      <c r="O60" s="25"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="25"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="25"/>
+      <c r="N60" s="25"/>
+      <c r="O60" s="26"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="22"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="25"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="26"/>
     </row>
     <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="22"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="24"/>
-      <c r="J62" s="24"/>
-      <c r="K62" s="24"/>
-      <c r="L62" s="24"/>
-      <c r="M62" s="24"/>
-      <c r="N62" s="24"/>
-      <c r="O62" s="25"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="25"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="26"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="22"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="24"/>
-      <c r="J63" s="24"/>
-      <c r="K63" s="24"/>
-      <c r="L63" s="24"/>
-      <c r="M63" s="24"/>
-      <c r="N63" s="24"/>
-      <c r="O63" s="25"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="25"/>
+      <c r="L63" s="25"/>
+      <c r="M63" s="25"/>
+      <c r="N63" s="25"/>
+      <c r="O63" s="26"/>
     </row>
     <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="22"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="24"/>
-      <c r="J64" s="24"/>
-      <c r="K64" s="24"/>
-      <c r="L64" s="24"/>
-      <c r="M64" s="24"/>
-      <c r="N64" s="24"/>
-      <c r="O64" s="25"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="25"/>
+      <c r="L64" s="25"/>
+      <c r="M64" s="25"/>
+      <c r="N64" s="25"/>
+      <c r="O64" s="26"/>
     </row>
     <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="22"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-      <c r="H65" s="24"/>
-      <c r="I65" s="24"/>
-      <c r="J65" s="24"/>
-      <c r="K65" s="24"/>
-      <c r="L65" s="24"/>
-      <c r="M65" s="24"/>
-      <c r="N65" s="24"/>
-      <c r="O65" s="25"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="25"/>
+      <c r="K65" s="25"/>
+      <c r="L65" s="25"/>
+      <c r="M65" s="25"/>
+      <c r="N65" s="25"/>
+      <c r="O65" s="26"/>
     </row>
     <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="22"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="24"/>
-      <c r="I66" s="24"/>
-      <c r="J66" s="24"/>
-      <c r="K66" s="24"/>
-      <c r="L66" s="24"/>
-      <c r="M66" s="24"/>
-      <c r="N66" s="24"/>
-      <c r="O66" s="25"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="25"/>
+      <c r="L66" s="25"/>
+      <c r="M66" s="25"/>
+      <c r="N66" s="25"/>
+      <c r="O66" s="26"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="22"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-      <c r="I67" s="24"/>
-      <c r="J67" s="24"/>
-      <c r="K67" s="24"/>
-      <c r="L67" s="24"/>
-      <c r="M67" s="24"/>
-      <c r="N67" s="24"/>
-      <c r="O67" s="25"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25"/>
+      <c r="J67" s="25"/>
+      <c r="K67" s="25"/>
+      <c r="L67" s="25"/>
+      <c r="M67" s="25"/>
+      <c r="N67" s="25"/>
+      <c r="O67" s="26"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="26"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="28"/>
-      <c r="K68" s="28"/>
-      <c r="L68" s="28"/>
-      <c r="M68" s="28"/>
-      <c r="N68" s="28"/>
-      <c r="O68" s="29"/>
+      <c r="A68" s="27"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="85">
   <si>
     <t>Table 1</t>
   </si>
@@ -118,10 +118,13 @@
     <t>`ALUOp_SUB</t>
   </si>
   <si>
+    <t>`SpecialOP_BEQ</t>
+  </si>
+  <si>
     <t>bne</t>
   </si>
   <si>
-    <t>`ALUOp_BNE</t>
+    <t>`SpecialOP_BNE</t>
   </si>
   <si>
     <t>j</t>
@@ -251,6 +254,18 @@
   </si>
   <si>
     <t>nop</t>
+  </si>
+  <si>
+    <t>bgtz</t>
+  </si>
+  <si>
+    <t>`SpecialOP_BGTZ</t>
+  </si>
+  <si>
+    <t>blez</t>
+  </si>
+  <si>
+    <t>`SpecialOP_BLEZ</t>
   </si>
 </sst>
 </file>
@@ -625,7 +640,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -702,6 +717,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -2172,12 +2190,12 @@
         <v>34</v>
       </c>
       <c r="O9" t="s" s="13">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" t="s" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="15">
         <v>5</v>
@@ -2216,15 +2234,15 @@
         <v>20</v>
       </c>
       <c r="N10" t="s" s="16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O10" t="s" s="13">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" t="s" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="15">
         <v>2</v>
@@ -2271,7 +2289,7 @@
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" t="s" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="15">
         <v>3</v>
@@ -2310,15 +2328,15 @@
         <v>0</v>
       </c>
       <c r="N12" t="s" s="21">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O12" t="s" s="13">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" t="s" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="15">
         <v>0</v>
@@ -2336,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s" s="16">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H13" s="17">
         <v>0</v>
@@ -2357,15 +2375,15 @@
         <v>0</v>
       </c>
       <c r="N13" t="s" s="11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O13" t="s" s="13">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" t="s" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15">
         <v>24</v>
@@ -2407,12 +2425,12 @@
         <v>21</v>
       </c>
       <c r="O14" t="s" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="s" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="15">
         <v>25</v>
@@ -2454,15 +2472,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" t="s" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s" s="18">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="16">
         <v>17</v>
@@ -2498,7 +2516,7 @@
         <v>27</v>
       </c>
       <c r="N16" t="s" s="16">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O16" t="s" s="13">
         <v>22</v>
@@ -2506,7 +2524,7 @@
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="s" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="15">
         <v>23</v>
@@ -2553,7 +2571,7 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="s" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="15">
         <v>0</v>
@@ -2592,7 +2610,7 @@
         <v>20</v>
       </c>
       <c r="N18" t="s" s="16">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O18" t="s" s="13">
         <v>22</v>
@@ -2600,7 +2618,7 @@
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="s" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="15">
         <v>0</v>
@@ -2639,7 +2657,7 @@
         <v>20</v>
       </c>
       <c r="N19" t="s" s="16">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O19" t="s" s="13">
         <v>22</v>
@@ -2647,10 +2665,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="s" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s" s="18">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s" s="16">
         <v>17</v>
@@ -2686,7 +2704,7 @@
         <v>27</v>
       </c>
       <c r="N20" t="s" s="16">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O20" t="s" s="13">
         <v>22</v>
@@ -2694,7 +2712,7 @@
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="s" s="14">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="15">
         <v>0</v>
@@ -2706,7 +2724,7 @@
         <v>17</v>
       </c>
       <c r="E21" t="s" s="16">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F21" s="17">
         <v>0</v>
@@ -2733,7 +2751,7 @@
         <v>20</v>
       </c>
       <c r="N21" t="s" s="16">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O21" t="s" s="13">
         <v>22</v>
@@ -2741,10 +2759,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="s" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s" s="18">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s" s="16">
         <v>17</v>
@@ -2780,7 +2798,7 @@
         <v>20</v>
       </c>
       <c r="N22" t="s" s="16">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O22" t="s" s="13">
         <v>22</v>
@@ -2788,10 +2806,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="s" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s" s="18">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="16">
         <v>17</v>
@@ -2827,7 +2845,7 @@
         <v>27</v>
       </c>
       <c r="N23" t="s" s="16">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O23" t="s" s="13">
         <v>22</v>
@@ -2835,7 +2853,7 @@
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="s" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B24" s="15">
         <v>0</v>
@@ -2847,7 +2865,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="s" s="16">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F24" s="17">
         <v>0</v>
@@ -2874,7 +2892,7 @@
         <v>27</v>
       </c>
       <c r="N24" t="s" s="16">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O24" t="s" s="13">
         <v>22</v>
@@ -2882,7 +2900,7 @@
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>
@@ -2921,7 +2939,7 @@
         <v>20</v>
       </c>
       <c r="N25" t="s" s="16">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O25" t="s" s="13">
         <v>22</v>
@@ -2929,7 +2947,7 @@
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" t="s" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="15">
         <v>0</v>
@@ -2968,7 +2986,7 @@
         <v>20</v>
       </c>
       <c r="N26" t="s" s="16">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O26" t="s" s="13">
         <v>22</v>
@@ -2976,7 +2994,7 @@
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" t="s" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B27" s="15">
         <v>28</v>
@@ -2994,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s" s="16">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H27" s="19">
         <v>0</v>
@@ -3018,12 +3036,12 @@
         <v>21</v>
       </c>
       <c r="O27" t="s" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" t="s" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B28" s="15">
         <v>29</v>
@@ -3041,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s" s="16">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H28" s="19">
         <v>0</v>
@@ -3065,15 +3083,15 @@
         <v>21</v>
       </c>
       <c r="O28" t="s" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" t="s" s="14">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s" s="18">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s" s="16">
         <v>17</v>
@@ -3088,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s" s="16">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H29" s="19">
         <v>0</v>
@@ -3117,7 +3135,7 @@
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" t="s" s="14">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" s="15">
         <v>0</v>
@@ -3164,7 +3182,7 @@
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" t="s" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B31" s="15">
         <v>0</v>
@@ -3211,7 +3229,7 @@
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" t="s" s="14">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="15">
         <v>20</v>
@@ -3253,12 +3271,12 @@
         <v>21</v>
       </c>
       <c r="O32" t="s" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" t="s" s="14">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B33" s="15">
         <v>0</v>
@@ -3297,7 +3315,7 @@
         <v>20</v>
       </c>
       <c r="N33" t="s" s="16">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O33" t="s" s="13">
         <v>22</v>
@@ -3305,7 +3323,7 @@
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" t="s" s="14">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="15">
         <v>0</v>
@@ -3343,7 +3361,7 @@
       <c r="M34" s="17">
         <v>0</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="20">
         <v>0</v>
       </c>
       <c r="O34" s="22">
@@ -3351,38 +3369,98 @@
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="26"/>
+      <c r="A35" t="s" s="14">
+        <v>81</v>
+      </c>
+      <c r="B35" s="15">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0</v>
+      </c>
+      <c r="G35" s="17">
+        <v>0</v>
+      </c>
+      <c r="H35" s="17">
+        <v>1</v>
+      </c>
+      <c r="I35" s="17">
+        <v>0</v>
+      </c>
+      <c r="J35" s="17">
+        <v>0</v>
+      </c>
+      <c r="K35" s="17">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M35" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N35" t="s" s="21">
+        <v>40</v>
+      </c>
+      <c r="O35" t="s" s="13">
+        <v>82</v>
+      </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="23"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="25"/>
-      <c r="N36" s="25"/>
-      <c r="O36" s="26"/>
+      <c r="A36" t="s" s="14">
+        <v>83</v>
+      </c>
+      <c r="B36" s="15">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="F36" s="17">
+        <v>0</v>
+      </c>
+      <c r="G36" s="17">
+        <v>0</v>
+      </c>
+      <c r="H36" s="17">
+        <v>1</v>
+      </c>
+      <c r="I36" s="17">
+        <v>0</v>
+      </c>
+      <c r="J36" s="17">
+        <v>0</v>
+      </c>
+      <c r="K36" s="17">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M36" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N36" t="s" s="21">
+        <v>40</v>
+      </c>
+      <c r="O36" t="s" s="13">
+        <v>84</v>
+      </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
       <c r="A37" s="23"/>
@@ -3398,8 +3476,8 @@
       <c r="K37" s="25"/>
       <c r="L37" s="25"/>
       <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="27"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="23"/>
@@ -3416,7 +3494,7 @@
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
       <c r="N38" s="25"/>
-      <c r="O38" s="26"/>
+      <c r="O38" s="27"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
       <c r="A39" s="23"/>
@@ -3433,7 +3511,7 @@
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
       <c r="N39" s="25"/>
-      <c r="O39" s="26"/>
+      <c r="O39" s="27"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
       <c r="A40" s="23"/>
@@ -3450,7 +3528,7 @@
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="N40" s="25"/>
-      <c r="O40" s="26"/>
+      <c r="O40" s="27"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
       <c r="A41" s="23"/>
@@ -3467,7 +3545,7 @@
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
       <c r="N41" s="25"/>
-      <c r="O41" s="26"/>
+      <c r="O41" s="27"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
       <c r="A42" s="23"/>
@@ -3484,7 +3562,7 @@
       <c r="L42" s="25"/>
       <c r="M42" s="25"/>
       <c r="N42" s="25"/>
-      <c r="O42" s="26"/>
+      <c r="O42" s="27"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="23"/>
@@ -3501,7 +3579,7 @@
       <c r="L43" s="25"/>
       <c r="M43" s="25"/>
       <c r="N43" s="25"/>
-      <c r="O43" s="26"/>
+      <c r="O43" s="27"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
       <c r="A44" s="23"/>
@@ -3518,7 +3596,7 @@
       <c r="L44" s="25"/>
       <c r="M44" s="25"/>
       <c r="N44" s="25"/>
-      <c r="O44" s="26"/>
+      <c r="O44" s="27"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="23"/>
@@ -3535,7 +3613,7 @@
       <c r="L45" s="25"/>
       <c r="M45" s="25"/>
       <c r="N45" s="25"/>
-      <c r="O45" s="26"/>
+      <c r="O45" s="27"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="23"/>
@@ -3552,7 +3630,7 @@
       <c r="L46" s="25"/>
       <c r="M46" s="25"/>
       <c r="N46" s="25"/>
-      <c r="O46" s="26"/>
+      <c r="O46" s="27"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="23"/>
@@ -3569,7 +3647,7 @@
       <c r="L47" s="25"/>
       <c r="M47" s="25"/>
       <c r="N47" s="25"/>
-      <c r="O47" s="26"/>
+      <c r="O47" s="27"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
       <c r="A48" s="23"/>
@@ -3586,7 +3664,7 @@
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
       <c r="N48" s="25"/>
-      <c r="O48" s="26"/>
+      <c r="O48" s="27"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="23"/>
@@ -3603,7 +3681,7 @@
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
       <c r="N49" s="25"/>
-      <c r="O49" s="26"/>
+      <c r="O49" s="27"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
       <c r="A50" s="23"/>
@@ -3620,7 +3698,7 @@
       <c r="L50" s="25"/>
       <c r="M50" s="25"/>
       <c r="N50" s="25"/>
-      <c r="O50" s="26"/>
+      <c r="O50" s="27"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
       <c r="A51" s="23"/>
@@ -3637,7 +3715,7 @@
       <c r="L51" s="25"/>
       <c r="M51" s="25"/>
       <c r="N51" s="25"/>
-      <c r="O51" s="26"/>
+      <c r="O51" s="27"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
       <c r="A52" s="23"/>
@@ -3654,7 +3732,7 @@
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
       <c r="N52" s="25"/>
-      <c r="O52" s="26"/>
+      <c r="O52" s="27"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
       <c r="A53" s="23"/>
@@ -3671,7 +3749,7 @@
       <c r="L53" s="25"/>
       <c r="M53" s="25"/>
       <c r="N53" s="25"/>
-      <c r="O53" s="26"/>
+      <c r="O53" s="27"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
       <c r="A54" s="23"/>
@@ -3688,7 +3766,7 @@
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
       <c r="N54" s="25"/>
-      <c r="O54" s="26"/>
+      <c r="O54" s="27"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
       <c r="A55" s="23"/>
@@ -3705,7 +3783,7 @@
       <c r="L55" s="25"/>
       <c r="M55" s="25"/>
       <c r="N55" s="25"/>
-      <c r="O55" s="26"/>
+      <c r="O55" s="27"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
       <c r="A56" s="23"/>
@@ -3722,7 +3800,7 @@
       <c r="L56" s="25"/>
       <c r="M56" s="25"/>
       <c r="N56" s="25"/>
-      <c r="O56" s="26"/>
+      <c r="O56" s="27"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
       <c r="A57" s="23"/>
@@ -3739,7 +3817,7 @@
       <c r="L57" s="25"/>
       <c r="M57" s="25"/>
       <c r="N57" s="25"/>
-      <c r="O57" s="26"/>
+      <c r="O57" s="27"/>
     </row>
     <row r="58" ht="19.5" customHeight="1">
       <c r="A58" s="23"/>
@@ -3756,7 +3834,7 @@
       <c r="L58" s="25"/>
       <c r="M58" s="25"/>
       <c r="N58" s="25"/>
-      <c r="O58" s="26"/>
+      <c r="O58" s="27"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
       <c r="A59" s="23"/>
@@ -3773,7 +3851,7 @@
       <c r="L59" s="25"/>
       <c r="M59" s="25"/>
       <c r="N59" s="25"/>
-      <c r="O59" s="26"/>
+      <c r="O59" s="27"/>
     </row>
     <row r="60" ht="19.5" customHeight="1">
       <c r="A60" s="23"/>
@@ -3790,7 +3868,7 @@
       <c r="L60" s="25"/>
       <c r="M60" s="25"/>
       <c r="N60" s="25"/>
-      <c r="O60" s="26"/>
+      <c r="O60" s="27"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
       <c r="A61" s="23"/>
@@ -3807,7 +3885,7 @@
       <c r="L61" s="25"/>
       <c r="M61" s="25"/>
       <c r="N61" s="25"/>
-      <c r="O61" s="26"/>
+      <c r="O61" s="27"/>
     </row>
     <row r="62" ht="19.5" customHeight="1">
       <c r="A62" s="23"/>
@@ -3824,7 +3902,7 @@
       <c r="L62" s="25"/>
       <c r="M62" s="25"/>
       <c r="N62" s="25"/>
-      <c r="O62" s="26"/>
+      <c r="O62" s="27"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
       <c r="A63" s="23"/>
@@ -3841,7 +3919,7 @@
       <c r="L63" s="25"/>
       <c r="M63" s="25"/>
       <c r="N63" s="25"/>
-      <c r="O63" s="26"/>
+      <c r="O63" s="27"/>
     </row>
     <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="23"/>
@@ -3858,7 +3936,7 @@
       <c r="L64" s="25"/>
       <c r="M64" s="25"/>
       <c r="N64" s="25"/>
-      <c r="O64" s="26"/>
+      <c r="O64" s="27"/>
     </row>
     <row r="65" ht="19.5" customHeight="1">
       <c r="A65" s="23"/>
@@ -3875,7 +3953,7 @@
       <c r="L65" s="25"/>
       <c r="M65" s="25"/>
       <c r="N65" s="25"/>
-      <c r="O65" s="26"/>
+      <c r="O65" s="27"/>
     </row>
     <row r="66" ht="19.5" customHeight="1">
       <c r="A66" s="23"/>
@@ -3892,7 +3970,7 @@
       <c r="L66" s="25"/>
       <c r="M66" s="25"/>
       <c r="N66" s="25"/>
-      <c r="O66" s="26"/>
+      <c r="O66" s="27"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="23"/>
@@ -3909,24 +3987,24 @@
       <c r="L67" s="25"/>
       <c r="M67" s="25"/>
       <c r="N67" s="25"/>
-      <c r="O67" s="26"/>
+      <c r="O67" s="27"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="27"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="29"/>
-      <c r="O68" s="30"/>
+      <c r="A68" s="28"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
+      <c r="N68" s="30"/>
+      <c r="O68" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -94,22 +94,22 @@
     <t>addiu</t>
   </si>
   <si>
+    <t>addu</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>`ALUOp_AND</t>
+  </si>
+  <si>
+    <t>andi</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>`EXT_ZERO</t>
-  </si>
-  <si>
-    <t>addu</t>
-  </si>
-  <si>
-    <t>and</t>
-  </si>
-  <si>
-    <t>`ALUOp_AND</t>
-  </si>
-  <si>
-    <t>andi</t>
-  </si>
-  <si>
-    <t>c</t>
   </si>
   <si>
     <t>beq</t>
@@ -1996,7 +1996,7 @@
         <v>25</v>
       </c>
       <c r="M5" t="s" s="16">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N5" t="s" s="16">
         <v>21</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" t="s" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="15">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" t="s" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="15">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>20</v>
       </c>
       <c r="N7" t="s" s="16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O7" t="s" s="13">
         <v>22</v>
@@ -2101,10 +2101,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" t="s" s="14">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s" s="18">
         <v>31</v>
-      </c>
-      <c r="B8" t="s" s="18">
-        <v>32</v>
       </c>
       <c r="C8" t="s" s="16">
         <v>17</v>
@@ -2137,10 +2137,10 @@
         <v>25</v>
       </c>
       <c r="M8" t="s" s="16">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N8" t="s" s="16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" t="s" s="13">
         <v>22</v>
@@ -2513,7 +2513,7 @@
         <v>25</v>
       </c>
       <c r="M16" t="s" s="16">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N16" t="s" s="16">
         <v>51</v>
@@ -2701,7 +2701,7 @@
         <v>25</v>
       </c>
       <c r="M20" t="s" s="16">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N20" t="s" s="16">
         <v>56</v>
@@ -2842,7 +2842,7 @@
         <v>25</v>
       </c>
       <c r="M23" t="s" s="16">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N23" t="s" s="16">
         <v>61</v>
@@ -2889,7 +2889,7 @@
         <v>19</v>
       </c>
       <c r="M24" t="s" s="16">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N24" t="s" s="16">
         <v>61</v>

--- a/scripts/mips32_r2000_instruction_set.xlsx
+++ b/scripts/mips32_r2000_instruction_set.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
   <si>
     <t>Table 1</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>`SpecialOP_BLEZ</t>
+  </si>
+  <si>
+    <t>bgezal</t>
+  </si>
+  <si>
+    <t>`SpecialOP_BGEZAL</t>
   </si>
 </sst>
 </file>
@@ -3463,21 +3469,51 @@
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="27"/>
+      <c r="A37" t="s" s="14">
+        <v>85</v>
+      </c>
+      <c r="B37" s="15">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="F37" s="17">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s" s="16">
+        <v>18</v>
+      </c>
+      <c r="H37" s="17">
+        <v>1</v>
+      </c>
+      <c r="I37" s="17">
+        <v>0</v>
+      </c>
+      <c r="J37" s="17">
+        <v>0</v>
+      </c>
+      <c r="K37" s="17">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="M37" t="s" s="16">
+        <v>20</v>
+      </c>
+      <c r="N37" t="s" s="21">
+        <v>40</v>
+      </c>
+      <c r="O37" t="s" s="13">
+        <v>86</v>
+      </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="23"/>
@@ -3493,7 +3529,7 @@
       <c r="K38" s="25"/>
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
-      <c r="N38" s="25"/>
+      <c r="N38" s="26"/>
       <c r="O38" s="27"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
